--- a/src/data/norm_positive_data.xlsx
+++ b/src/data/norm_positive_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\ナイトレイン\RelicSim\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825F7E4B-1A32-4459-8A1A-45BD5F0E1559}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D93E0E-F803-453D-8174-51023075270B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17460" xr2:uid="{01B957CF-7FB2-450A-BC7D-D4F7B1CDF751}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="1005">
   <si>
     <t>最大HP上昇</t>
   </si>
@@ -3088,6 +3088,143 @@
   </si>
   <si>
     <t>norm_366</t>
+  </si>
+  <si>
+    <t>大教会の強敵を倒す度、最大HP上昇</t>
+  </si>
+  <si>
+    <t>norm_d01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺跡の強敵を倒す度、神秘上昇</t>
+  </si>
+  <si>
+    <t>norm_d02</t>
+  </si>
+  <si>
+    <t>【 追跡者 】精神力上昇、生命力低下</t>
+  </si>
+  <si>
+    <t>norm_d03</t>
+  </si>
+  <si>
+    <t>【 追跡者 】知力/信仰上昇、筋力/技量低下</t>
+  </si>
+  <si>
+    <t>norm_d04</t>
+  </si>
+  <si>
+    <t>【 守護者 】筋力/技量上昇、生命力低下</t>
+  </si>
+  <si>
+    <t>norm_d05</t>
+  </si>
+  <si>
+    <t>【 守護者 】精神力/信仰上昇、生命力低下</t>
+  </si>
+  <si>
+    <t>norm_d06</t>
+  </si>
+  <si>
+    <t>【 鉄の目 】生命力/筋力上昇、技量低下</t>
+  </si>
+  <si>
+    <t>norm_d07</t>
+  </si>
+  <si>
+    <t>【 鉄の目 】神秘上昇、技量低下</t>
+  </si>
+  <si>
+    <t>norm_d08</t>
+  </si>
+  <si>
+    <t>【 レディ 】生命力/筋力上昇、精神力低下</t>
+  </si>
+  <si>
+    <t>norm_d09</t>
+  </si>
+  <si>
+    <t>【 レディ 】精神力/信仰上昇、知力低下</t>
+  </si>
+  <si>
+    <t>norm_d10</t>
+  </si>
+  <si>
+    <t>【 無頼漢 】精神力/知力上昇、生命力/持久力低下</t>
+  </si>
+  <si>
+    <t>norm_d11</t>
+  </si>
+  <si>
+    <t>【 無頼漢 】神秘上昇、生命力低下</t>
+  </si>
+  <si>
+    <t>norm_d12</t>
+  </si>
+  <si>
+    <t>【 復讐者 】生命力/持久力上昇、精神力低下</t>
+  </si>
+  <si>
+    <t>norm_d13</t>
+  </si>
+  <si>
+    <t>【 復讐者 】筋力上昇、信仰低下</t>
+  </si>
+  <si>
+    <t>norm_d14</t>
+  </si>
+  <si>
+    <t>【 隠者 】生命力/持久力/技量上昇、知力/信仰低下</t>
+  </si>
+  <si>
+    <t>norm_d15</t>
+  </si>
+  <si>
+    <t>【 隠者 】知力/信仰上昇、精神力低下</t>
+  </si>
+  <si>
+    <t>norm_d16</t>
+  </si>
+  <si>
+    <t>【 執行者 】生命力/持久力上昇、神秘低下</t>
+  </si>
+  <si>
+    <t>norm_d17</t>
+  </si>
+  <si>
+    <t>【 執行者 】技量/神秘上昇、生命力低下</t>
+  </si>
+  <si>
+    <t>norm_d18</t>
+  </si>
+  <si>
+    <t>【 学者 】精神力上昇、生命力低下</t>
+  </si>
+  <si>
+    <t>norm_d19</t>
+  </si>
+  <si>
+    <t>【 学者 】持久力/技量上昇、知力/神秘低下</t>
+  </si>
+  <si>
+    <t>norm_d20</t>
+  </si>
+  <si>
+    <t>【 葬儀屋 】技量上昇、生命力/信仰低下</t>
+  </si>
+  <si>
+    <t>norm_d21</t>
+  </si>
+  <si>
+    <t>【 葬儀屋 】精神力/信仰上昇、筋力低下</t>
+  </si>
+  <si>
+    <t>norm_d22</t>
+  </si>
+  <si>
+    <t>コレクター効果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3493,7 +3630,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5652F1F-E407-4292-BEE7-B704C971ECE6}">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A2:L367"/>
+  <dimension ref="A2:L389"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="47.125" bestFit="1" customWidth="1"/>
@@ -10756,6 +10893,314 @@
       </c>
       <c r="G367" s="4" t="s">
         <v>404</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>961</v>
+      </c>
+      <c r="B368" t="s">
+        <v>960</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D368" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>963</v>
+      </c>
+      <c r="B369" t="s">
+        <v>962</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>965</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D370" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>967</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D371" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>969</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>971</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D373" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>973</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D374" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>975</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>977</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D376" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>979</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>981</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D378" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>983</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D379" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>985</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D380" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>987</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>989</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D382" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>991</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>993</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>995</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D385" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>997</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D386" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>999</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D387" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D388" s="4" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C389" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D389" s="4" t="s">
+        <v>1004</v>
       </c>
     </row>
   </sheetData>
